--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_3_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_3_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8287</v>
+        <v>2.6668</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2204</v>
+        <v>3.8233</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3917</v>
+        <v>-1.1564</v>
       </c>
       <c r="G2" t="n">
         <v>2.8751</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7938</v>
+        <v>0.6319</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1325</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3387</v>
+        <v>-0.1034</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3871</v>
+        <v>1.1588</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8066</v>
+        <v>0.2168</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5805</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-1.604</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.473</v>
+        <v>0.2447</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5272</v>
+        <v>-0.0626</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9458</v>
+        <v>0.3073</v>
       </c>
       <c r="V3" t="n">
         <v>2.2862</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4805</v>
+        <v>-1.0485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7983</v>
+        <v>2.2685</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2787</v>
+        <v>-3.317</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.6819</v>
+        <v>0.7775</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5305</v>
+        <v>0.754</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1514</v>
+        <v>0.0235</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5583</v>
+        <v>3.9587</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6687</v>
+        <v>2.3527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1104</v>
+        <v>1.606</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1236</v>
+        <v>-3.1812</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8618</v>
+        <v>-1.5987</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2618</v>
+        <v>-1.5825</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4154</v>
+        <v>-0.7538</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3566</v>
+        <v>-0.5305</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0589</v>
+        <v>-0.2234</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2232</v>
+        <v>-1.0878</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1219</v>
+        <v>-1.5046</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3451</v>
+        <v>0.4168</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1096</v>
+        <v>-2.4941</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3963</v>
+        <v>-0.1151</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7133</v>
+        <v>-2.379</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9861</v>
+        <v>-1.4183</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2239</v>
+        <v>0.1176</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2378</v>
+        <v>-1.5359</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0957</v>
+        <v>-1.0759</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6203</v>
+        <v>-0.2327</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4755</v>
+        <v>-0.8431</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7266</v>
+        <v>-0.2379</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1537</v>
+        <v>-0.0863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5729</v>
+        <v>-0.1516</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>0.2525</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4491</v>
+        <v>-1.3061</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9331</v>
+        <v>-0.0274</v>
       </c>
       <c r="F7" t="n">
-        <v>0.484</v>
+        <v>-1.2787</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4941</v>
+        <v>-3.6819</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1151</v>
+        <v>-1.5305</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.379</v>
+        <v>-2.1514</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4183</v>
+        <v>-0.5583</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1176</v>
+        <v>-0.6687</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5359</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0759</v>
+        <v>-3.1236</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2327</v>
+        <v>-0.8618</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8431</v>
+        <v>-2.2618</v>
       </c>
       <c r="P7" t="n">
         <v>1.3917</v>
@@ -1000,28 +1000,28 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5992</v>
+        <v>0.5898</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5149</v>
+        <v>0.5309</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0843</v>
+        <v>0.0589</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2525</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2525</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.839</v>
+        <v>-1.5888</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3125</v>
+        <v>-0.3037</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5266</v>
+        <v>-1.2851</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0639</v>
+        <v>0.6889</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8736</v>
+        <v>0.5952</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8097</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6579</v>
+        <v>2.8302</v>
       </c>
       <c r="K8" t="n">
-        <v>2.464</v>
+        <v>2.0474</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1939</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5941</v>
+        <v>-2.1413</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5904</v>
+        <v>-1.4522</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0037</v>
+        <v>-0.6891</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5988</v>
+        <v>-0.5612</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>-0.5619</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5715</v>
+        <v>0.0007</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>-0.7886</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>-0.2525</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9408</v>
+        <v>-1.7041</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6787</v>
+        <v>-0.1573</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6195</v>
+        <v>-1.5468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7775</v>
+        <v>-2.1096</v>
       </c>
       <c r="H9" t="n">
-        <v>0.754</v>
+        <v>-0.3963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0235</v>
+        <v>-1.7133</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9587</v>
+        <v>0.9861</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3527</v>
+        <v>1.2239</v>
       </c>
       <c r="L9" t="n">
-        <v>1.606</v>
+        <v>-0.2378</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1812</v>
+        <v>-3.0957</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5987</v>
+        <v>-1.6203</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5825</v>
+        <v>-1.4755</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6461</v>
+        <v>0.2458</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.1254</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5258</v>
+        <v>0.3712</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RIVERO</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3256</v>
+        <v>-1.7307</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8799</v>
+        <v>-0.2378</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4456</v>
+        <v>-1.493</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7152</v>
+        <v>1.0639</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3673</v>
+        <v>1.8736</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.348</v>
+        <v>-0.8097</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4319</v>
+        <v>2.6579</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5055</v>
+        <v>2.464</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2834</v>
+        <v>-1.5941</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8618</v>
+        <v>-0.5904</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4216</v>
+        <v>-1.0037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5381</v>
+        <v>-0.4905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>0.0474</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0901</v>
+        <v>-0.5379</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. RIVERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5392</v>
+        <v>-1.9889</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0861</v>
+        <v>-1.644</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4531</v>
+        <v>-0.3448</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6889</v>
+        <v>-2.7152</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5952</v>
+        <v>-2.3673</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.348</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8302</v>
+        <v>-1.4319</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0474</v>
+        <v>-1.5055</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1413</v>
+        <v>-1.2834</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4522</v>
+        <v>-0.8618</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6891</v>
+        <v>-0.4216</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5116</v>
+        <v>-0.2014</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3443</v>
+        <v>-0.2122</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1674</v>
+        <v>0.0108</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6874</v>
+        <v>-2.2664</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7796</v>
+        <v>-1.4257</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9079</v>
+        <v>-0.8407</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7323</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1871</v>
+        <v>0.2339</v>
       </c>
       <c r="T12" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.3618</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.879800000000001</v>
+        <v>-8.506499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5599999999999989</v>
+        <v>0.9333999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.439799999999998</v>
+        <v>-9.4398</v>
       </c>
       <c r="G13" t="n">
         <v>-8.931699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2696</v>
+        <v>0.2696000000000002</v>
       </c>
       <c r="I13" t="n">
         <v>-9.201400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>15.0768</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7467999999999999</v>
+        <v>-0.3734</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3514999999999997</v>
+        <v>0.02190000000000014</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3952000000000003</v>
+        <v>-0.3952000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6805</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2401</v>
+        <v>3.3327</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8828</v>
+        <v>2.7344</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6425999999999999</v>
+        <v>0.5984</v>
       </c>
       <c r="G14" t="n">
-        <v>0.453</v>
+        <v>2.833</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4128</v>
+        <v>-1.3996</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0402</v>
+        <v>4.2326</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1728</v>
+        <v>3.1624</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7078</v>
+        <v>-0.6519</v>
       </c>
       <c r="L14" t="n">
-        <v>0.465</v>
+        <v>3.8143</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7198</v>
+        <v>-0.3294</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2949</v>
+        <v>-0.7477</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4248</v>
+        <v>0.4183</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8746</v>
+        <v>0.7343</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0474</v>
+        <v>0.59</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8272</v>
+        <v>0.1443</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1444</v>
+        <v>-0.9304</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8223</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9621</v>
+        <v>2.8362</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2812</v>
+        <v>3.6469</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3191</v>
+        <v>-0.8107</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1129</v>
+        <v>0.453</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4503</v>
+        <v>0.4128</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6626</v>
+        <v>0.0402</v>
       </c>
       <c r="J15" t="n">
-        <v>3.865</v>
+        <v>2.1728</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0921</v>
+        <v>1.7078</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7729</v>
+        <v>0.465</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7521</v>
+        <v>-1.7198</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6418</v>
+        <v>-1.2949</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1103</v>
+        <v>-0.4248</v>
       </c>
       <c r="P15" t="n">
         <v>-0.232</v>
@@ -1624,28 +1624,28 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4033</v>
+        <v>0.4707</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1019</v>
+        <v>-0.1885</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5052</v>
+        <v>0.6592</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.8223</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.881</v>
+        <v>2.659</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0298</v>
+        <v>3.0453</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8512</v>
+        <v>-0.3863</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8759</v>
+        <v>2.1129</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3961</v>
+        <v>1.4503</v>
       </c>
       <c r="I16" t="n">
-        <v>2.272</v>
+        <v>0.6626</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2089</v>
+        <v>3.865</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5945</v>
+        <v>3.0921</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8034</v>
+        <v>0.7729</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.333</v>
+        <v>-1.7521</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8016</v>
+        <v>-1.6418</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4685</v>
+        <v>-0.1103</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0025</v>
+        <v>0.1002</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9085</v>
+        <v>-0.3378</v>
       </c>
       <c r="U16" t="n">
-        <v>0.094</v>
+        <v>0.438</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4665</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8387</v>
+        <v>2.3306</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4985</v>
+        <v>1.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3403</v>
+        <v>1.0084</v>
       </c>
       <c r="G17" t="n">
-        <v>2.833</v>
+        <v>0.8759</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3996</v>
+        <v>-1.3961</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2326</v>
+        <v>2.272</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1624</v>
+        <v>1.2089</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6519</v>
+        <v>-0.5945</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8143</v>
+        <v>1.8034</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3294</v>
+        <v>-0.333</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7477</v>
+        <v>-0.8016</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>0.4685</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2403</v>
+        <v>0.452</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3541</v>
+        <v>0.2008</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1138</v>
+        <v>0.2513</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9304</v>
+        <v>1.4665</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4447</v>
+        <v>2.0509</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5318</v>
+        <v>2.0036</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0871</v>
+        <v>0.0473</v>
       </c>
       <c r="G18" t="n">
         <v>1.4218</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.673</v>
+        <v>-0.0668</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>0.0237</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3916</v>
+        <v>0.1735</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8796</v>
+        <v>1.1444</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.488</v>
+        <v>-0.9708</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2842</v>
+        <v>1.7101</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1285</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4127</v>
+        <v>1.141</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3996</v>
+        <v>3.4622</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8654</v>
+        <v>2.0537</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4658</v>
+        <v>1.4085</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6838</v>
+        <v>-1.7521</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7369</v>
+        <v>-1.4845</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9469</v>
+        <v>-0.2676</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8381999999999999</v>
+        <v>-0.467</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3383</v>
+        <v>-0.5344</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4999</v>
+        <v>0.0674</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0795</v>
+        <v>0.1392</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7905</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.87</v>
+        <v>-0.6224</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7101</v>
+        <v>-1.2842</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5691000000000001</v>
+        <v>1.1285</v>
       </c>
       <c r="I20" t="n">
-        <v>1.141</v>
+        <v>-2.4127</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4622</v>
+        <v>0.3996</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0537</v>
+        <v>1.8654</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4085</v>
+        <v>-1.4658</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7521</v>
+        <v>-1.6838</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4845</v>
+        <v>-0.7369</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2676</v>
+        <v>-0.9469</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.72</v>
+        <v>0.5858</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8883</v>
+        <v>0.2203</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1683</v>
+        <v>0.3655</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3037</v>
+        <v>-0.8034</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6473</v>
+        <v>-1.237</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3436</v>
+        <v>0.4336</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0556</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0561</v>
+        <v>0.5564</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2819</v>
+        <v>0.6921</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2258</v>
+        <v>-0.1357</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4678</v>
+        <v>-0.8616</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0212</v>
+        <v>0.4506</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4466</v>
+        <v>-1.3122</v>
       </c>
       <c r="G22" t="n">
         <v>2.0664</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7714</v>
+        <v>-0.1652</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6642</v>
+        <v>-0.1924</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1072</v>
+        <v>0.0272</v>
       </c>
       <c r="V22" t="n">
         <v>0.2525</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5108</v>
+        <v>-1.0168</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9183</v>
+        <v>-2.6824</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4075</v>
+        <v>1.6656</v>
       </c>
       <c r="G23" t="n">
         <v>0.2748</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9274</v>
+        <v>-0.4334</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4872</v>
+        <v>-0.2291</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5167</v>
+        <v>-1.1743</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8678</v>
+        <v>-1.7498</v>
       </c>
       <c r="F24" t="n">
-        <v>0.351</v>
+        <v>0.5755</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4765</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5764</v>
+        <v>-0.2339</v>
       </c>
       <c r="T24" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5843</v>
+        <v>-0.3598</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.8797</v>
+        <v>9.666</v>
       </c>
       <c r="E25" t="n">
-        <v>9.439599999999999</v>
+        <v>9.439699999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5597999999999999</v>
+        <v>0.2264</v>
       </c>
       <c r="G25" t="n">
         <v>8.9316</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2696000000000001</v>
+        <v>-0.2695999999999998</v>
       </c>
       <c r="I25" t="n">
-        <v>9.201300000000002</v>
+        <v>9.2013</v>
       </c>
       <c r="J25" t="n">
         <v>19.1235</v>
@@ -2404,13 +2404,13 @@
         <v>11.5977</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7467999999999999</v>
+        <v>1.5331</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3954</v>
+        <v>0.3954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3513999999999999</v>
+        <v>1.1378</v>
       </c>
       <c r="V25" t="n">
         <v>2.6805</v>
